--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_11_Full_122_Cau/Day_11_Ngan_Hang_Phan_06_20_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_11_Full_122_Cau/Day_11_Ngan_Hang_Phan_06_20_Cau.xlsx
@@ -675,7 +675,7 @@
       <c r="J4" s="3" t="n"/>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Người duyệt phải lần từ kết luận về bằng chứng cụ thể nào?</t>
+          <t>Báo cáo an toàn có thể kiểm toán phải cung cấp chuỗi bằng chứng hoàn chỉnh: truy vết từ ca kiểm thử/nguồn đầu vào → các lớp kiểm soát tương ứng → đích gửi/verifier độc lập, kèm tỷ lệ chặn nhầm và rủi ro còn lại.</t>
         </is>
       </c>
     </row>
@@ -757,7 +757,7 @@
       <c r="J6" s="3" t="n"/>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Nếu sai thì hệ quả là gì và có hoàn tác được không?</t>
+          <t>Tác vụ gợi ý sắp xếp ghi chú cá nhân có hệ quả thấp và người dùng có thể hoàn tác ngay lập tức, do đó mô hình HITL phù hợp là lấy mẫu kiểm tra định kỳ và thu thập phản hồi người dùng, không cần phê duyệt bắt buộc trước.</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       <c r="J8" s="3" t="n"/>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Confidence nói model chắc đến đâu; nó không quyết định hệ quả của hành động có được chấp nhận hay không.</t>
+          <t>Độ tự tin (confidence) của mô hình chỉ phản ánh sự chắc chắn về mặt toán học, không làm giảm mức độ nghiêm trọng của hậu quả; các hành động rủi ro cao bắt buộc phải có sự phê duyệt của con người theo quy định.</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,7 @@
       <c r="J10" s="3" t="n"/>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Yếu tố nào đo mức chắc chắn, còn yếu tố nào quyết định quyền thực thi hành động hệ quả cao?</t>
+          <t>Kể cả khi mô hình đạt confidence 99,9% và đã vượt qua bộ lọc nội dung, quyền thực thi đối với các hành động rủi ro cao vẫn không được phép tự động hóa mà bắt buộc phải có sự phê duyệt của con người.</t>
         </is>
       </c>
     </row>
@@ -969,7 +969,7 @@
       <c r="J11" s="3" t="n"/>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Người duyệt cần biết chính xác hành động nào sẽ được thực hiện, trên đối tượng nào và với hệ quả gì.</t>
+          <t>Giao diện phê duyệt không cung cấp đối tượng, đích đến hay nội dung thay đổi sẽ dẫn đến tình trạng duyệt mù; người duyệt bắt buộc phải được cung cấp đầy đủ gói ngữ cảnh để đưa ra quyết định có căn cứ.</t>
         </is>
       </c>
     </row>
@@ -1053,7 +1053,7 @@
       <c r="J13" s="3" t="n"/>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Trạng thái chờ duyệt không phải đã được duyệt.</t>
+          <t>Vòng đời Human-In-The-Loop (HITL) cho hành động rủi ro cao: Tạo yêu cầu chờ duyệt có thời hạn cụ thể (o2) → người duyệt xem xét để phê duyệt/từ chối hoặc yêu cầu tự hết hạn (o3) → nếu được duyệt thì thực thi đúng hành động, nếu từ chối thì hủy (o1) → ghi nhận kết quả cuối cùng vào audit log (o4).</t>
         </is>
       </c>
     </row>
@@ -1135,7 +1135,7 @@
       <c r="J15" s="3" t="n"/>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Người điều tra sự cố ghép các bản ghi bằng khóa nào?</t>
+          <t>Việc thiếu các mã định danh tương quan chung (`request_id` / `decision_id`) khiến nhật ký kiểm toán không thể liên kết chuỗi sự kiện từ đầu vào → guardrails → phê duyệt → hành động, làm mất khả năng điều tra sự cố.</t>
         </is>
       </c>
     </row>
@@ -1217,7 +1217,7 @@
       <c r="J17" s="3" t="n"/>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: So count trên cùng lưu lượng trước khi diễn giải.</t>
+          <t>Số lần chặn tăng gấp 2 lần nhưng lưu lượng request tăng gấp 4 lần có nghĩa là tỷ lệ chặn (block rate) thực tế đã giảm một nửa; cần đánh giá theo tỷ lệ trên mẫu số lưu lượng chứ không chỉ nhìn số đếm tuyệt đối.</t>
         </is>
       </c>
     </row>

--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_11_Full_122_Cau/Day_11_Ngan_Hang_Phan_06_20_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_11_Full_122_Cau/Day_11_Ngan_Hang_Phan_06_20_Cau.xlsx
@@ -624,10 +624,21 @@
       <c r="K3" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Bản sửa có bảo vệ được các bí mật cùng loại ngoài đúng chuỗi F8 không?
-Phân tích theo nguyên lý thiết kế: Bản sửa có bảo vệ được các bí mật cùng loại ngoài đúng chuỗi F8 không?</t>
+- [1.5 điểm] Phê bình chính xác bản sửa hiện tại là giải pháp chắp vá giòn gãy (brittle exact match), chỉ pass bài test F8 mà bất lực trước biến thể.
+- [1.5 điểm] Thiết kế giải pháp tổng quát: sử dụng bộ quét pattern/entropy (Presidio/TruffleHog) và ngăn chặn nạp bí mật vào context prompt.
+- [1.0 điểm] Xây dựng chu kỳ kiểm thử hồi quy đa dạng với các biến thể diễn đạt lại để đảm bảo tính bền vững của bản vá.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Đánh giá Bản sửa Hiện tại (Evaluation of Current Fix - Brittle Patch Anti-pattern):
+   - Đánh giá: Bản sửa là một 'Giải pháp chắp vá giòn gãy' (Fragile / Brittle String Matching Anti-pattern), hoàn toàn KHÔNG ĐẠT YÊU CẦU bảo mật thực tế.
+   - Nguyên nhân: Nhóm chỉ thêm danh sách chặn cho đúng một chuỗi ký tự cụ thể của F8 (Exact String Blocklist). Kẻ tấn công chỉ cần thay đổi định dạng, diễn đạt lại bằng từ đồng nghĩa, chèn khoảng trắng, dùng chữ hoa thường, hoặc mã hóa ký tự là bí mật tiếp tục bị rò rỉ. Đây là hành vi 'dạy cho bài thi' (overfitting to the test case) thay vì giải quyết gốc rễ của cơ chế sinh dữ liệu nhạy cảm.
+2. Thiết kế Chu kỳ Sửa chữa Tiếp theo Chuẩn mực (Generalized Remediation Cycle):
+   - Bước 1 (Generalized Semantic Detection): Thay vì so khớp chuỗi cố định, triển khai mô hình quét PII/Secret tổng quát (Regex entropy detector, Presidio, TruffleHog scanner) có khả năng nhận diện mẫu hình bí mật (API key structure, token format, UUID, thẻ tín dụng) bất kể giá trị cụ thể là gì.
+   - Bước 2 (Context-Level Redaction / Sanitization): Cắt đứt bí mật ngay từ đầu vào hoặc từ tool execution context, không nạp chuỗi bí mật thật vào LLM context prompt trừ khi có mã hóa bảo vệ.
+   - Bước 3 (Adversarial Paraphrase Benchmark): Xây dựng bộ test suite mới gồm hàng trăm biến thể diễn đạt lại (Paraphrased &amp; Obfuscated Variants) để kiểm chứng rằng bản vá mới có khả năng khái quát hóa và chặn đứng toàn bộ họ bí mật đó.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Bảo mật không thể đạt được bằng cách đuổi theo từng chuỗi ký tự vi phạm cụ thể (Whack-A-Mole approach). Khi phát hiện một lỗ hổng rò rỉ bí mật, bản sửa chữa phải mang tính 'Khái quát hóa theo chủng loại' (Generalized Category Defense). Chu kỳ khắc phục phải tập trung vào mẫu hình thực thể (Pattern &amp; Entropy), ranh giới truyền dữ liệu và kiểm thử đối kháng đa dạng thay vì chỉ vá một chuỗi ký tự để qua mắt bài test F8.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+OWASP Top 10 for LLM - LLM02: Sensitive Information Disclosure và Microsoft Presidio Architecture: https://microsoft.github.io/presidio/</t>
         </is>
       </c>
     </row>
@@ -706,10 +717,24 @@
       <c r="K5" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Lần theo 20 tình huống từ cổng đầu vào tới cổng gửi ra ngoài và số rò rỉ quan sát tại đích.
-Phân tích theo nguyên lý thiết kế: Lần theo 20 tình huống từ cổng đầu vào tới cổng gửi ra ngoài và số rò rỉ quan sát tại đích.</t>
+- [1.5 điểm] Lần theo chính xác số liệu qua từng chặng: 18/20 chặn ở input -&gt; 2 tới model -&gt; 2/2 chặn ở egress -&gt; 0 rò rỉ tại đích cuối.
+- [1.5 điểm] Đánh giá đầy đủ tác động phụ trên tập lành tính: 6/100 (6%) bị chặn nhầm.
+- [1.0 điểm] Đưa ra kết luận khách quan, chuẩn mực: khẳng định sự thành công của Defense-in-Depth nhưng chỉ rõ cần tinh chỉnh giảm false positives.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Báo cáo Đánh giá An toàn Từ Nguồn đến Đích gửi (Source-to-Sink Safety Report):
+1. Lần theo Luồng truyền 20 tình huống Indirect Injection:
+   - Tầng Cổng Đầu vào (Input Detection Gate): Tiếp nhận 20 tình huống -&gt; Chặn đứng thành công 18 tình huống (Hiệu quả đánh chặn sớm đạt 18/20 = 90.0%).
+   - Tầng Mô hình (Model Execution Context): Có 2 tình huống (10.0%) vượt qua được Input Gate và tiếp cận Model. Model bị thao túng và cố gắng kích hoạt công cụ exfiltration ra ngoài.
+   - Tầng Cổng Gửi ra ngoài (Egress Sink Gate): 2 tình huống độc hại này bị Cổng Egress phát hiện và CHẶN ĐỨNG HOÀN TOÀN (2/2 blocked, 100% phòng vệ tại ranh giới cuối).
+   - Số vụ rò rỉ quan sát được tại Đích gửi thực tế (Observed Exfiltrations at Sink) = 0 VỤ (Tỷ lệ rò rỉ thực tế đạt 0.0%).
+2. Đánh giá Tác động Nghiệp vụ trên Tập Lành tính (Benign Tradeoff):
+   - Tỷ lệ chặn nhầm (False Positive Rate): 6 / 100 = 6.0% tình huống lành tính bị chặn oan ở đầu vào, gây suy giảm trải nghiệm người dùng.
+3. Kết luận Toàn diện ở mức phù hợp:
+   - 'Kiến trúc Phòng thủ theo chiều sâu (Defense-in-Depth) đã chứng minh hiệu quả tuyệt đối trong việc ngăn chặn rò rỉ dữ liệu ra thế giới bên ngoài (Zero Egress Leakage), nhờ vào vai trò chốt chặn vững chắc của Cổng Egress khi Input Gate bị lọt 2 ca. Tuy nhiên, tỷ lệ chặn nhầm 6% là một khoảng trống vận hành cần được tối ưu hóa bằng cách tinh chỉnh ngưỡng nhạy của bộ phát hiện đầu vào'.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Báo cáo an toàn từ Nguồn đến Đích (Source-to-Sink Security Evaluation) cung cấp cái nhìn chân thực về hiệu quả của kiến trúc đa tầng. Việc một tầng phòng thủ đơn lẻ bị lọt lưới (Input Gate lọt 10%) không đồng nghĩa với việc hệ thống bị xâm nhập, chừng nào tầng chốt chặn tại Đích gửi (Egress Gate) vẫn hoàn thành xuất sắc nhiệm vụ. Báo cáo phải phản ánh khách quan cả hai mặt: an ninh tuyệt đối tại đích và chi phí suy giảm dịch vụ do chặn nhầm.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+NIST AI 100-2 E2023: Defense-in-Depth for AI Systems và OWASP Top 10 for LLM - Egress Controls and Verification</t>
         </is>
       </c>
     </row>
@@ -788,10 +813,20 @@
       <c r="K7" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Người duyệt cần hành động nào để phê duyệt, và hệ thống làm gì nếu quá hạn?
-Phân tích theo nguyên lý thiết kế: Người duyệt cần hành động nào để phê duyệt, và hệ thống làm gì nếu quá hạn?</t>
+- [1.5 điểm] Lựa chọn chính xác mô hình Active Synchronous Human Approval, lập luận thuyết phục dựa trên tính chất khó hoàn tác và bằng chứng bất định.
+- [1.5 điểm] Thiết lập SLA 10 phút và chính sách xử lý quá hạn Fail-Closed (tự động hủy yêu cầu đóng tài khoản khi timeout).
+- [1.0 điểm] Bảo đảm tính an toàn mặc định (Fail-safe default) bảo vệ tài khoản khách hàng và ghi log kiểm toán đầy đủ.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Chọn Mô hình HITL phù hợp (Human-in-the-Loop Model Selection):
+   - Lựa chọn: MÔ HÌNH PHÊ DUYỆT CHỦ ĐỘNG TRỰC TIẾP (Active Synchronous Human Approval / Human-in-the-Loop Gate). Tuyệt đối KHÔNG CHỌN Human-on-the-loop (hậu kiểm) hay tự động hóa hoàn toàn.
+   - Căn cứ: Đề bài nêu rõ ba đặc điểm rủi ro chí mạng: (a) Hành động đóng tài khoản là 'Khó hoàn tác' (Irreversible / High Consequence); (b) 'Bằng chứng còn bất định' (Uncertain Evidence / Low Confidence); (c) Rủi ro pháp lý và khách hàng rất lớn. Do đó, Agent CHỈ ĐƯỢC PHÉP tạo bản ghi yêu cầu đóng tài khoản ở trạng thái chờ; quyền thực thi xóa/đóng bắt buộc phải do nhân viên có thẩm quyền ký duyệt.
+2. Thiết lập SLA và Xử lý khi Quá hạn (Timeout Handling Policy):
+   - SLA Duyệt: Hạn chót phê duyệt nghiêm ngặt là 10 phút (SLA = 10 minutes timeout window).
+   - Hành vi hệ thống khi Quá hạn (Timeout Fallback): BẮT BUỘC ÁP DỤNG FAIL-CLOSED / AUTO-REJECT (Hủy yêu cầu tự động). Nếu sau 10 phút mà người duyệt không phản hồi: Hệ thống tự động chuyển trạng thái yêu cầu thành `EXPIRED_TIMEOUT`, hủy bỏ tác vụ đóng tài khoản, bảo toàn nguyên vẹn trạng thái tài khoản khách hàng, và ghi log cảnh báo tới người quản lý hàng đợi.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Khi một quyết định của AI có tính chất không thể đảo ngược (Irreversible) và dựa trên chứng cứ bất định, việc đưa con người vào vòng lặp kiểm soát chủ động (Active HITL) là yêu cầu an toàn bắt buộc. Trong các tình huống có áp lực thời gian (hạn chót 10 phút), chính sách xử lý khi hết hạn phải tuân thủ nguyên tắc an toàn mặc định (Fail-Safe Defaults): 'Thà từ chối một tác vụ chưa chắc chắn còn hơn tự động thực thi một hành vi phá hủy không thể cứu vãn'.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+NIST AI RMF 1.0 - Human-AI Teaming and Oversight Guidelines và EU AI Act: Requirements for Human Oversight (Article 14)</t>
         </is>
       </c>
     </row>
@@ -870,10 +905,21 @@
       <c r="K9" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Xếp rủi ro hành động trước, rồi mới dùng confidence và mức mới lạ để ưu tiên xử lý.
-Phân tích theo nguyên lý thiết kế: Xếp rủi ro hành động trước, rồi mới dùng confidence và mức mới lạ để ưu tiên xử lý.</t>
+- [1.5 điểm] Xếp đúng mức ưu tiên cho cả 4 trường hợp từ P1 đến P4 theo nguyên lý: Rủi ro cao/Confidence thấp là P1 cao nhất, Rủi ro thấp/Confidence cao là P4 tự động.
+- [1.5 điểm] Thiết kế tuyến xử lý phù hợp cho từng nhóm: Senior review khẩn cấp (P1), Duyệt tiêu chuẩn (P2), Rà soát học tập (P3), Tự động hóa lấy mẫu hậu kiểm (P4).
+- [1.0 điểm] Trình bày lý do kiến trúc chặt chẽ về việc tối ưu hóa nhân lực và bảo đảm an toàn đa tầng.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Thiết kế Ma trận Tuyến Xử lý và Mức Ưu tiên (Risk-Confidence Routing Matrix):
+Nguyên tắc cốt lõi: 'Mức độ rủi ro của hành động (Action Consequence Risk) quyết định tuyến kiểm soát; Độ tin cậy (Confidence) và Mức độ mới lạ (Novelty) quyết định thứ tự ưu tiên xử lý trong hàng đợi'.
+1. Tuyến cho 4 trường hợp cụ thể:
+   - Trường hợp 1: Rủi ro Cao / Confidence Thấp -&gt; TUYẾN: KHẨN CẤP ĐẶC BIỆT (Critical Escalation Gate). Mức ưu tiên: P1 (CAO NHẤT). Xử lý: Chuyển ngay lập tức đến Chuyên viên an toàn / Senior Reviewer có thẩm quyền cao nhất để phân tích chuyên sâu trước khi ra quyết định.
+   - Trường hợp 2: Rủi ro Cao / Confidence Cao -&gt; TUYẾN: KIỂM SOÁT TIÊU CHUẨN (Standard Synchronous Approval). Mức ưu tiên: P2 (ƯU TIÊN CAO). Xử lý: Vẫn bắt buộc con người duyệt vì hành động rủi ro cao, nhưng nhân viên chỉ cần rà soát nhanh các bằng chứng rõ ràng do độ tin cậy đã cao.
+   - Trường hợp 3: Rủi ro Thấp / Confidence Thấp và Mới lạ -&gt; TUYẾN: HÀNG ĐỢI RÀ SOÁT HỌC TẬP (Active Learning / Quality Assurance Queue). Mức ưu tiên: P3 (TRUNG BÌNH). Xử lý: Hành động có thể tạm hoãn hoặc chạy ở chế độ an toàn, chuyển chuyên gia phân tích để cập nhật tri thức mới cho hệ thống.
+   - Trường hợp 4: Rủi ro Thấp / Confidence Cao -&gt; TUYẾN: TỰ ĐỘNG HÓA HOÀN TOÀN (Autonomous Fast-Track Execution). Mức ưu tiên: P4 (TỰ ĐỘNG - KHÔNG CẦN DUYỆT TRỰC TIẾP). Xử lý: Agent tự thực thi ngay lập tức; lấy mẫu ngẫu nhiên 1% phục vụ hậu kiểm (Post-audit Sampling).
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Định tuyến tác vụ dựa trên Rủi ro và Độ tin cậy (Risk-Confidence Routing) là giải pháp tối ưu hóa nguồn lực con người trong hệ thống HITL. Nếu dồn mọi việc cho con người duyệt, hàng đợi sẽ tắc nghẽn; ngược lại nếu thả lỏng, thảm họa sẽ xảy ra. Bằng cách phân tầng ma trận 2x2, hệ thống tự động hóa an toàn các tác vụ ít rủi ro/độ tin cậy cao, đồng thời tập trung năng lực chuyên gia tinh nhuệ nhất vào các ca rủi ro cao/độ tin cậy thấp (P1).
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Google Research - 'Human-in-the-Loop Machine Learning' (Robert Munro) và NIST AI RMF - Human Oversight Governance</t>
         </is>
       </c>
     </row>
@@ -1000,10 +1046,27 @@
       <c r="K12" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Người duyệt cần thấy phần thay đổi, hai nguồn mâu thuẫn và hệ quả của việc chấp nhận hoặc giữ nguyên.
-Phân tích theo nguyên lý thiết kế: Người duyệt cần thấy phần thay đổi, hai nguồn mâu thuẫn và hệ quả của việc chấp nhận hoặc giữ nguyên.</t>
+- [1.5 điểm] Thiết kế đầy đủ các thành phần cốt lõi: Diff view trực quan giữa v7 và v8, đối chứng 2 nguồn mâu thuẫn kèm trích đoạn và cấp thẩm quyền.
+- [1.5 điểm] Phân tích rõ ràng hệ quả của hai nhánh quyết định (chấp nhận v8 vs giữ nguyên v7).
+- [1.0 điểm] Đảm bảo nguyên lý chống quá tải nhận thức: súc tích, có giao diện quyết định nhanh, không nhồi nhét tài liệu thừa.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Thiết kế Gói Ngữ cảnh Tối thiểu cho Người duyệt (Minimal Context Package Design):
+Để tránh quá tải nhận thức (Cognitive Overload), gói ngữ cảnh chỉ hiển thị các thông tin cốt tử có tính quyết định, loại bỏ toàn bộ dữ liệu nền không liên quan:
+1. Phần Hiển thị Sai khác (Visual Semantic Diff View):
+   - Hiển thị trực quan song song (Side-by-side Diff): Tô đỏ các điều khoản bị xóa/sửa trong Policy P3 phiên bản v7 và tô xanh các điều khoản mới được đề xuất trong phiên bản v8.
+2. Hai Nguồn Mâu thuẫn (Conflicting Sources Juxtaposition):
+   - Nguồn A: Tên nguồn, cấp độ thẩm quyền (ví dụ: Công văn Pháp chế số 12), ngày ban hành và đoạn trích dẫn trực tiếp chứa căn cứ A;
+   - Nguồn B: Tên nguồn, cấp độ thẩm quyền (ví dụ: Hướng dẫn Vận hành Nhân sự), ngày ban hành và đoạn trích dẫn trực tiếp chứa căn cứ B;
+   - Chỉ ra điểm xung đột trực tiếp: Nêu rõ 1 câu tóm tắt điểm mâu thuẫn cốt lõi giữa A và B mà Agent không thể tự hòa giải.
+3. Hệ quả Dự kiến (Action Consequence &amp; Tradeoff Preview):
+   - Hệ quả nếu Chấp nhận cập nhật sang v8: Nhóm đối tượng bị ảnh hưởng, quyền lợi thay đổi;
+   - Hệ quả nếu Giữ nguyên v7: Rủi ro không tuân thủ quy định mới nếu có.
+4. Tùy chọn Quyết định Một Chạm (One-Click Decision Interface):
+   - Nút: `[Chấp nhận v8]` / `[Giữ nguyên v7]` / `[Yêu cầu Pháp chế làm rõ]` kèm ô nhập lý do ngắn gọn.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Người duyệt trong quy trình HITL thường bị kiệt sức nếu phải đọc toàn bộ tài liệu gốc dài hàng chục trang (Cognitive Fatigue). Thiết kế gói ngữ cảnh tối thiểu (Minimal Context Package) tập trung vào nguyên lý 'Bản đồ chênh lệch và Nguồn đối chứng': Chỉ cung cấp đúng phần sai khác (Diff), đoạn trích mâu thuẫn kèm siêu dữ liệu xuất xứ và hệ quả của từng lựa chọn, giúp chuyên viên đưa ra quyết định chính xác trong thời gian ngắn nhất.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Google People + AI Guidebook (PAIR) - Design for Human-AI Interaction &amp; Review Interfaces: https://pair.withgoogle.com/chapter/human-review/</t>
         </is>
       </c>
     </row>
@@ -1084,10 +1147,25 @@
       <c r="K14" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Approval cấp cho action nào và còn hiệu lực ở commit time không?
-Phân tích theo nguyên lý thiết kế: Approval cấp cho action nào và còn hiệu lực ở commit time không?</t>
+- [1.5 điểm] Phân tích chính xác sự vi phạm kép: hết hạn thời gian thực thi (14:02 &gt; 14:00) và vi phạm phạm vi do agent đổi tham số sau phê duyệt.
+- [1.5 điểm] Đưa ra quyết định chuẩn mực: HỦY VÀ TỪ CHỐI THỰC THI (Abort/Reject) ngay lập tức.
+- [1.0 điểm] Khẳng định nguyên tắc bất biến: phê duyệt chỉ gắn với hash tham số ban đầu, mọi đột biến đều vô hiệu hóa chữ ký.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Phân tích vòng đời phê duyệt và Ra quyết định cho Yêu cầu H9:
+1. Phân tích Trạng thái và Thời hạn (Temporal Validity Analysis):
+   - Thời hạn phê duyệt quy định: Hết hạn lúc 14:00 (TTL = 14:00).
+   - Thời điểm Reviewer nhấn duyệt: 13:59 (Thỏa mãn thời hạn ban đầu, còn 1 phút).
+   - Thời điểm Executor chạy thực tế (Commit / Execution Time): 14:02 (ĐÃ QUÁ HẠN 2 PHÚT). Nguyên tắc giao dịch quy định: Ủy quyền chỉ hợp lệ nếu quá trình thực thi bắt đầu trước khi TTL hết hạn. Tại thời điểm 14:02, phê duyệt đã rơi vào trạng thái `EXPIRED`.
+2. Phân tích Phạm vi Tham số (Scope Tampering / Parameter Mutation):
+   - 'Tham số hành động bị Agent đổi sau khi phê duyệt' -&gt; ĐÂY LÀ HÀNH VI VI PHẠM TÍNH TOÀN VẸN NGHIÊM TRỌNG (Critical Integrity Violation / Scope Invalidation).
+   - Reviewer cấp quyền cho tập tham số `P_old`, nhưng Agent lại cố tình thực thi tập tham số `P_new`. Phê duyệt đã bị vô hiệu hóa hoàn toàn vì đối tượng được duyệt không còn khớp với hành động thực tế.
+3. Quyết định của Hệ thống (Final Decision):
+   - TỪ CHỐI THỰC THI VÀ HỦY GIAO DỊCH NGAY LẬP TỨC (ABORT &amp; REJECT TRANSACTION).
+   - Hành động bảo mật: Khóa yêu cầu H9 với mã lỗi `AUTHORIZATION_PARAM_MUTATION_AND_TIMEOUT`, phát cảnh báo P1 cho Đội An ninh về hành vi Agent tự ý sửa đổi tham số sau lưng người duyệt.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Trong vòng đời phê duyệt HITL, 'Ủy quyền là một hợp đồng bất biến gắn liền với Hash của Tham số và Thời hạn hiệu lực' (Cryptographic Action Binding). Bất kỳ sự thay đổi nào đối với tham số hành động sau khi người duyệt đã ký (Post-approval parameter tampering) hoặc việc thực thi diễn ra sau khi hạn chót đã trôi qua đều lập tức hủy bỏ tính hợp pháp của lệnh gọi. Executor bắt buộc phải từ chối thi hành để ngăn chặn các cuộc tấn công chiếm đoạt quyền.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+OAuth 2.0 Token Revocation and Proof-of-Possession Standards (RFC 7009 / RFC 7800) và OWASP LLM08: Excessive Agency Controls</t>
         </is>
       </c>
     </row>
@@ -1166,10 +1244,42 @@
       <c r="K16" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Thông tin nào cần để ghép toàn bộ lượt xử lý, và PII nào cần rút gọn trước khi ghi log?
-Phân tích theo nguyên lý thiết kế: Thông tin nào cần để ghép toàn bộ lượt xử lý, và PII nào cần rút gọn trước khi ghi log?</t>
+- [1.5 điểm] Thiết kế cơ chế liên kết chuỗi toàn diện bằng correlation_id xuyên suốt mọi giai đoạn xử lý.
+- [1.5 điểm] Xây dựng giải pháp bảo vệ PII trong log chuẩn mực: băm có muối (pseudonymization) và gắn nhãn che giấu (redaction).
+- [1.0 điểm] Cung cấp schema JSON audit trail hoàn chỉnh, sạch sẽ và có tính ứng dụng cao.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Thiết kế Schema Audit Trail liên kết chuỗi xử lý và Bảo vệ Quyền riêng tư PII:
+1. Cơ chế Ghép chuỗi Xử lý (Distributed Tracing &amp; Correlation):
+   - Sử dụng một khóa định danh tương quan duy nhất `correlation_id` (W3C Trace Context Traceparent) được truyền xuyên suốt qua mọi trạm: Request Ingestion -&gt; Normalization -&gt; Guardrails -&gt; Human Review -&gt; Model Response.
+2. Cơ chế Bảo vệ Quyền riêng tư (Privacy-Preserving PII Handling):
+   - Tuyệt đối không ghi PII thô (Raw PII) vào bảng log hệ thống tập trung;
+   - Kỹ thuật Băm một chiều có Muối (Salted SHA-256 Pseudonymization): Chuyển đổi các định danh nhạy cảm (như CCCD, Email, Phone) thành chuỗi băm để vẫn có thể phân tích hành vi và đối soát mà không lộ danh tính;
+   - Kỹ thuật Che giấu (Redaction/Token Masking): Thay thế các chuỗi PII trong văn bản bằng token phân loại: `[PHONE_REDACTED]`, `[EMAIL_REDACTED]`.
+3. Cấu trúc Schema Audit (Audit Trail Record Schema):
+```json
+{
+  "correlation_id": "c4b9-8e21-4f10",
+  "timestamp_iso": "2026-10-23T15:00:00Z",
+  "user_pseudonym": "salt_hash_9f82a1",
+  "normalized_input_masked": "Tôi muốn kiểm tra gói bảo hiểm cho số điện thoại [PHONE_REDACTED]",
+  "guardrail_verdicts": {
+    "input_safety": "PASS",
+    "pii_scanner": "FOUND_AND_MASKED",
+    "jailbreak_detector": "PASS"
+  },
+  "human_review_event": {
+    "required": false,
+    "reviewer_id": null,
+    "decision": null
+  },
+  "output_payload_masked": "Gói bảo hiểm của bạn hiện đang có hiệu lực đến 2027.",
+  "execution_latency_ms": 245
+}
+```
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nhật ký kiểm toán an toàn (Safety Audit Trail) phải giải quyết hài hòa hai yêu cầu mâu thuẫn: (1) Tính truy vết toàn diện (Full Traceability) để phục vụ điều tra sự cố; và (2) Tuân thủ luật bảo vệ dữ liệu cá nhân (GDPR/HIPAA Compliance). Bằng cách sử dụng `correlation_id` để kết nối các mắt xích phân tán và áp dụng kỹ thuật mặt nạ hóa/băm giả định danh (Pseudonymization &amp; Masking), hệ thống duy trì khả năng kiểm toán mà không biến log thành kho rò rỉ dữ liệu.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+W3C Trace Context Specification: https://www.w3.org/TR/trace-context/ và ISO/IEC 27001 Annex A.12.4: Logging and Monitoring</t>
         </is>
       </c>
     </row>
@@ -1248,10 +1358,22 @@
       <c r="K18" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Tách điều đã quan sát được khỏi nguyên nhân mà số liệu chưa chứng minh.
-Phân tích theo nguyên lý thiết kế: Tách điều đã quan sát được khỏi nguyên nhân mà số liệu chưa chứng minh.</t>
+- [1.5 điểm] Thiết kế cảnh báo phân cấp chính xác: Alert P1 cho lỗi Judge (20% vs ngưỡng 5%) và Alert P2 cho tỷ lệ chặn tăng (8% vs nền 2%).
+- [1.5 điểm] Xây dựng quy trình xử lý ban đầu chuẩn: ưu tiên khôi phục năng lực của Judge service và kích hoạt fallback.
+- [1.0 điểm] Phân tích sâu sắc giới hạn kết luận: số lần rate limit không đổi chỉ ra nguyên nhân nhiều khả năng do lỗi nội bộ chứ chưa đủ căn cứ quy chụp cho tấn công bên ngoài.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Thiết kế Cảnh báo Dựa trên Dữ liệu Thực nghiệm (Empirical Alert Design):
+   - Alert 1 (Cảnh báo Đỏ - P1 High Severity): 'Tỷ lệ Lỗi của Safety Judge Tăng Vọt Bất Thường' (Safety Judge Error Surge). Giá trị đo được: 20% lỗi (gấp 4 lần ngưỡng cho phép 5%). Đây là sự cố hạ tầng khẩn cấp khiến rào chắn kiểm duyệt an toàn bị mất năng lực.
+   - Alert 2 (Cảnh báo Vàng - P2 Medium Severity): 'Tỷ lệ Chặn Yêu cầu Tăng Cao' (Block Rate Anomaly). Giá trị đo được: 8% (gấp 4 lần mức nền thông thường 2%).
+2. Cách Xử lý Ban đầu (Initial Triage Runbook):
+   - Bước 1: Ưu tiên xử lý lỗi của Safety Judge trước. Kiểm tra log của Judge service (nguyên nhân gây 20% fail: cạn quota API, timeout mạng, hay payload lỗi gây crash) và kích hoạt Local Fallback Judge để duy trì rào chắn an toàn.
+   - Bước 2: Điều tra xem tỷ lệ chặn 8% tăng lên có phải là hệ quả giả mạo do Judge bị lỗi chuyển sang chế độ Fail-Closed chặn hàng loạt hay không; hoặc kiểm tra mẫu các request bị chặn để phát hiện chiến dịch tấn công diện rộng.
+3. Giới hạn của Kết luận (Limits of Inference):
+   - Cần phân biệt rõ: Số liệu hiện tại CHƯA ĐỦ ĐỂ KẾT LUẬN hệ thống đang bị tấn công DDoS hay bị spam tấn công, bởi vì 'Số lần Rate Limit không đổi' (Rate limit violations remain flat). Sự tăng đột biến của tỷ lệ chặn nhiều khả năng bắt nguồn từ chính sự cố hỏng hóc nội bộ của Judge hơn là một cuộc tấn công lưu lượng từ bên ngoài.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Trong giám sát an toàn (Safety Observability), kỹ sư phải thận trọng tách biệt giữa 'Hiện tượng quan sát được' (Symptoms) và 'Nguyên nhân thực tế' (Root Causes). Tỷ lệ chặn tăng gấp 4 lần đi kèm tỷ lệ lỗi Judge tăng gấp 4 lần, trong khi Rate Limit không biến động, là dấu hiệu kinh điển của lỗi nội bộ hệ thống kiểm duyệt (Internal Subsystem Failure) dẫn đến chặn nhầm lan tràn. Xử lý hạ tầng Judge là ưu tiên số một trước khi kết luận về tấn công bên ngoài.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Google SRE Book - Monitoring Distributed Systems &amp; Practical Alerting: https://sre.google/sre-book/monitoring-distributed-systems/ và Arize Phoenix Realtime Monitoring</t>
         </is>
       </c>
     </row>
@@ -1330,10 +1452,25 @@
       <c r="K20" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Mỗi nhóm lỗi chỉ ra control nào cần sửa; đừng mặc định mọi phản hồi đều là dữ liệu để huấn luyện model.
-Phân tích theo nguyên lý thiết kế: Mỗi nhóm lỗi chỉ ra control nào cần sửa; đừng mặc định mọi phản hồi đều là dữ liệu để huấn luyện model.</t>
+- [1.5 điểm] Ánh xạ chính xác cả 3 nhóm lỗi sang đúng control cần sửa: 12 ca chỉnh threshold, 5 ca sửa prompt/few-shot, 3 ca cải tiến UI gói ngữ cảnh.
+- [1.5 điểm] Bác bỏ rõ ràng tư duy sai lầm về việc đem mọi lỗi đi huấn luyện lại mô hình nền (no blind model retraining).
+- [1.0 điểm] Thiết lập phương pháp kiểm chứng độc lập cho từng nhóm sửa đổi để xác nhận khắc phục triệt để.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Ánh xạ Phản hồi sang Cập nhật Controls tương ứng (Feedback-to-Control Mapping):
+   - Nhóm 1 (12 lỗi do Ngưỡng Detector quá thấp - Threshold Mismatch):
+     + Cập nhật Control: KHÔNG fine-tune lại model! Hành động: Tinh chỉnh lại ngưỡng cắt quyết định (Operating Decision Threshold) của mô hình phân loại an toàn trên đường cong ROC/PR curve, nâng độ nhạy (Recall) lên để bắt trọn các ca vi phạm này.
+   - Nhóm 2 (5 lỗi do Chỉ dẫn trong Prompt Mơ hồ - Ambiguous System Prompt):
+     + Cập nhật Control: Bổ sung chỉ thị tường minh (Prompt Disambiguation) trong System Prompt/Guardrails Configuration; bổ sung các ví dụ Few-Shot định nghĩa rõ ràng các trường hợp ranh giới cần chặn.
+   - Nhóm 3 (3 lỗi do Người duyệt thiếu Ngữ cảnh nguồn - Context Deficit in Review UI):
+     + Cập nhật Control: Cải tiến Giao diện Người duyệt (HITL Reviewer UI Enhancement); bổ sung cửa sổ hiển thị nguồn trích dẫn gốc và các bằng chứng đối chiếu trực tiếp vào gói duyệt để chuyên viên không phải phỏng đoán.
+2. Cách Kiểm chứng Hiệu quả (Verification &amp; Regression Testing):
+   - Đối với Nhóm 1: Chạy lại bộ kiểm thử benchmark trên 12 ca lỗi cũ cùng tập dữ liệu chuẩn, xác nhận độ nhạy đạt 100% trong khi tỷ lệ False Positive vẫn trong hạn mức cho phép;
+   - Đối với Nhóm 2: Chạy unit test prompt với 5 kịch bản mơ hồ, xác nhận Agent phản hồi chuẩn mực theo chính sách mới;
+   - Đối với Nhóm 3: Thực hiện kiểm thử chấp nhận người dùng (UAT) với đội ngũ Reviewer, xác nhận 100% ngữ cảnh nguồn hiển thị đầy đủ và thời gian xử lý ca duyệt giảm.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Một sai lầm tai hại trong vận hành AI là 'Coi mọi phản hồi của con người như dữ liệu huấn luyện lại mô hình' (Blindly Retraining Anti-pattern). Trong 20 lỗi trên, không có lỗi nào cần huấn luyện lại trọng số mô hình: 60% lỗi là do cấu hình ngưỡng quyết định, 25% là do kỹ thuật soạn prompt, và 15% là do thiết kế công cụ giao diện người dùng. Phân loại chính xác nguồn gốc lỗi giúp cập nhật đúng cơ chế kiểm soát với chi phí thấp nhất và thời gian triển khai nhanh nhất.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Google SRE Book - Postmortem Culture &amp; Action Item Prioritization: https://sre.google/sre-book/postmortem-culture/ và Human-in-the-Loop Machine Learning (Munro)</t>
         </is>
       </c>
     </row>
@@ -1412,10 +1549,25 @@
       <c r="K22" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Tính lượng vào hàng duyệt sau khi tự xử lý 20%, rồi giữ riêng cổng bắt buộc cho rủi ro cao.
-Phân tích theo nguyên lý thiết kế: Tính lượng vào hàng duyệt sau khi tự xử lý 20%, rồi giữ riêng cổng bắt buộc cho rủi ro cao.</t>
+- [1.5 điểm] Tính toán chính xác các thông số hàng đợi: lưu lượng vào sau giảm 20% là đúng 40 ca/giờ, cân bằng hoàn hảo với năng lực duyệt 40 ca/giờ.
+- [1.5 điểm] Bảo toàn tuyệt đối cổng chất lượng bắt buộc: 100% trường hợp rủi ro cao phải qua người duyệt.
+- [1.0 điểm] Xây dựng phương án giải tỏa dứt điểm 600 ca tồn đọng cũ (burst capacity) và kiểm toán lấy mẫu hậu kiểm cho luồng tự động.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Tính toán Lưu lượng và Cân bằng Hàng đợi (Throughput &amp; Bottleneck Calculations):
+   - Lưu lượng tiếp nhận mới: 50 trường hợp/giờ.
+   - Chính sách tự xử lý: 20% trường hợp rủi ro thấp được phép tự động xử lý (Auto-resolve Fast Track).
+     + Lưu lượng tự xử lý = 50 * 20% = 10 trường hợp/giờ.
+   - Lưu lượng thực tế đi vào hàng đợi duyệt của con người: `50 - 10 = 40 trường hợp/giờ`.
+   - Năng lực duyệt tối đa của đội ngũ Reviewer: 40 trường hợp/giờ.
+   - Cân bằng dòng chảy ổn định (Steady-State Influx): `Lưu lượng vào (40/h) == Năng lực xử lý (40/h)`. Như vậy, việc kích hoạt cơ chế tự xử lý 20% rủi ro thấp đã giúp ngăn chặn việc hàng đợi tiếp tục phình to không kiểm soát (chấm dứt tình trạng thâm hụt tích lũy 10 ca/giờ).
+2. Đề xuất Hướng Xử lý Toàn diện Giữ vững Cổng Chất lượng:
+   - Bảo vệ Cổng Chất lượng Bắt buộc (Mandatory High-Risk Quality Gate): 100% các trường hợp rủi ro cao (High-risk Cases) BẮT BUỘC phải giữ lại trong hàng đợi để con người duyệt, tuyệt đối không được tự động hóa.
+   - Giải tỏa Hàng đợi Tồn đọng (Drain the 600 Backlog): Hiện tại vẫn còn 600 trường hợp tồn đọng cũ. Để giải tỏa, triển khai cơ chế Tăng cường Năng lực Tạm thời (Temporary Burst Capacity): Huy động thêm nhân sự ngoài giờ hoặc overtime để tăng năng lực duyệt lên 60 ca/giờ trong vòng 30 giờ (dư 20 ca/h * 30h = giải tỏa sạch 600 ca tồn đọng).
+   - Giám sát Chất lượng Tự động (Automated Quality Auditing): Lấy mẫu ngẫu nhiên 5% các ca rủi ro thấp đã tự xử lý để kiểm tra chéo hậu kiểm, đảm bảo quy tắc phân loại rủi ro hoạt động chính xác.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Giải quyết nút thắt cổ chai trong hàng đợi HITL đòi hỏi tư duy phân tích hệ thống hàng đợi (Queueing Theory): Tách biệt dòng công việc dựa trên ma trận rủi ro để giảm lưu lượng đầu vào (Net Influx) ngang bằng với năng lực xử lý (Capacity). Bằng cách tự động hóa các ca rủi ro thấp được phép, hệ thống đạt trạng thái cân bằng bền vững trong khi vẫn duy trì 100% rào chắn an toàn cho các tác vụ nhạy cảm, kết hợp kế hoạch giải tỏa tồn đọng có định lượng rõ ràng.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Operations Research &amp; Queueing Systems (Kleinrock) và Google SRE Book - Managing Critical State and Queueing Delay</t>
         </is>
       </c>
     </row>
